--- a/DataVaryingTemperature/3MaterialsTempDependent.xlsx
+++ b/DataVaryingTemperature/3MaterialsTempDependent.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Krishnan Suresh\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\DataVaryingTemperature\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\DataVaryingTemperature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EA2F629-4CA5-4E89-8894-61FC96AE1E44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372888C3-63E7-44B1-9D12-F8037E3B3BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -138,9 +138,6 @@
     <t>K0</t>
   </si>
   <si>
-    <t>T_Limit</t>
-  </si>
-  <si>
     <t>Criticality</t>
   </si>
   <si>
@@ -154,6 +151,9 @@
   </si>
   <si>
     <t>K3</t>
+  </si>
+  <si>
+    <t>Temp_Limit</t>
   </si>
 </sst>
 </file>
@@ -544,22 +544,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="20.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="14" style="1" customWidth="1"/>
     <col min="3" max="3" width="11" style="1" customWidth="1"/>
-    <col min="4" max="6" width="9.140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="12.42578125" style="1" customWidth="1"/>
-    <col min="8" max="10" width="11.5703125" style="1" customWidth="1"/>
-    <col min="11" max="14" width="10.42578125" style="1" customWidth="1"/>
+    <col min="4" max="6" width="9.109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.44140625" style="1" customWidth="1"/>
+    <col min="8" max="10" width="11.5546875" style="1" customWidth="1"/>
+    <col min="11" max="14" width="10.44140625" style="1" customWidth="1"/>
     <col min="15" max="15" width="10" style="1" customWidth="1"/>
     <col min="16" max="16" width="14" style="1" customWidth="1"/>
-    <col min="17" max="705" width="20.5703125" style="1" customWidth="1"/>
-    <col min="706" max="16384" width="9.140625" style="1"/>
+    <col min="17" max="705" width="20.5546875" style="1" customWidth="1"/>
+    <col min="706" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="8" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" s="8" customFormat="1" ht="18" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
         <v>4</v>
       </c>
@@ -594,22 +594,22 @@
         <v>30</v>
       </c>
       <c r="M1" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="Q1" s="8" t="s">
-        <v>32</v>
-      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
@@ -656,10 +656,10 @@
         <v>29</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>14</v>
       </c>
@@ -712,7 +712,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>23</v>
       </c>
@@ -765,7 +765,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" ht="18" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
@@ -791,13 +791,13 @@
         <v>300000000</v>
       </c>
       <c r="I5" s="7">
-        <v>100000000</v>
+        <v>10000000</v>
       </c>
       <c r="J5" s="7">
-        <v>2000000</v>
+        <v>20000</v>
       </c>
       <c r="K5" s="6">
-        <v>100000</v>
+        <v>1000</v>
       </c>
       <c r="L5" s="7">
         <v>190</v>
@@ -827,12 +827,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECC80EBF-8B96-4896-8C13-AD8A976D05A3}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.5703125" customWidth="1"/>
+    <col min="1" max="1" width="15.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -846,7 +846,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -860,7 +860,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -874,7 +874,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -888,7 +888,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>

--- a/DataVaryingTemperature/3MaterialsTempDependent.xlsx
+++ b/DataVaryingTemperature/3MaterialsTempDependent.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\Personal\suresh\Software\Github\ERSL-Private\METALS\DataVaryingTemperature\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372888C3-63E7-44B1-9D12-F8037E3B3BA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E199FAB6-00E0-4DDC-9AE9-E8E1A70A0E7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1776" yWindow="1956" windowWidth="20604" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -193,7 +193,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -227,11 +227,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -261,6 +276,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -663,35 +684,35 @@
       <c r="A3" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="B3" s="2">
-        <v>8000</v>
+      <c r="B3" s="11">
+        <v>7850</v>
       </c>
       <c r="C3" s="2">
         <v>6</v>
       </c>
-      <c r="D3" s="5">
-        <v>120000000000</v>
+      <c r="D3" s="12">
+        <v>210000000000</v>
       </c>
       <c r="E3" s="5">
         <v>100000000000</v>
       </c>
       <c r="F3" s="5">
-        <v>90000000000</v>
+        <v>9000000000</v>
       </c>
       <c r="G3" s="5">
-        <v>80000000000</v>
-      </c>
-      <c r="H3" s="7">
-        <v>900000000</v>
+        <v>800000000</v>
+      </c>
+      <c r="H3" s="12">
+        <v>250000000</v>
       </c>
       <c r="I3" s="7">
-        <v>800000000</v>
+        <v>80000000</v>
       </c>
       <c r="J3" s="7">
-        <v>700000000</v>
+        <v>7000000</v>
       </c>
       <c r="K3" s="7">
-        <v>650000000</v>
+        <v>650000</v>
       </c>
       <c r="L3" s="7">
         <v>18</v>
@@ -716,35 +737,35 @@
       <c r="A4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="11">
         <v>7800</v>
       </c>
       <c r="C4" s="3">
         <v>4</v>
       </c>
-      <c r="D4" s="6">
-        <v>110000000000</v>
+      <c r="D4" s="12">
+        <v>200000000000</v>
       </c>
       <c r="E4" s="6">
-        <v>100000000000</v>
+        <v>90000000000</v>
       </c>
       <c r="F4" s="6">
-        <v>90000000000</v>
+        <v>5000000000</v>
       </c>
       <c r="G4" s="6">
-        <v>80000000000</v>
-      </c>
-      <c r="H4" s="7">
-        <v>700000000</v>
+        <v>400000000</v>
+      </c>
+      <c r="H4" s="12">
+        <v>180000000</v>
       </c>
       <c r="I4" s="7">
-        <v>600000000</v>
+        <v>60000000</v>
       </c>
       <c r="J4" s="7">
-        <v>550000000</v>
+        <v>5500000</v>
       </c>
       <c r="K4" s="7">
-        <v>500000000</v>
+        <v>500000</v>
       </c>
       <c r="L4" s="7">
         <v>50</v>
@@ -769,14 +790,14 @@
       <c r="A5" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="11">
         <v>2700</v>
       </c>
       <c r="C5" s="3">
         <v>2</v>
       </c>
-      <c r="D5" s="6">
-        <v>40000000000</v>
+      <c r="D5" s="12">
+        <v>70000000000</v>
       </c>
       <c r="E5" s="6">
         <v>30000000000</v>
@@ -787,8 +808,8 @@
       <c r="G5" s="6">
         <v>200000</v>
       </c>
-      <c r="H5" s="7">
-        <v>300000000</v>
+      <c r="H5" s="12">
+        <v>100000000</v>
       </c>
       <c r="I5" s="7">
         <v>10000000</v>
